--- a/resources/one-person-ai-business/files/opab-adv-price-rise-calculator.xlsx
+++ b/resources/one-person-ai-business/files/opab-adv-price-rise-calculator.xlsx
@@ -17,10 +17,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,11 +67,6 @@
       <color rgb="000C2733"/>
       <sz val="11"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -98,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,8 +118,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -514,7 +507,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -545,7 +537,6 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -597,7 +588,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -670,7 +660,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -699,7 +688,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -713,10 +701,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/one-person-ai-business/files/opab-adv-price-rise-calculator.xlsx
+++ b/resources/one-person-ai-business/files/opab-adv-price-rise-calculator.xlsx
@@ -698,7 +698,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
